--- a/inventory/files/2026-W40/STA_CA_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_CA_AUTO_2026-W40.xlsx
@@ -1539,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="17"/>
   <cols>
     <col width="26.5" customWidth="1" style="14" min="1" max="1"/>
@@ -1690,61 +1690,61 @@
     <row r="9" customFormat="1" s="17">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AH-HLKITA</t>
+          <t>AH-TRKITA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4796</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AH-RCTIRE10A</t>
+          <t>AH-RCPL-B14A</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1225</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AH-RCPL-B14A</t>
+          <t>AH-HLKITA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1015</v>
+        <v>795</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-MICRTOWEL12A</t>
+          <t>AH-RCTIRE10A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>116</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AH-RCWHL14A</t>
+          <t>AH-VEHSHAM16A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AH-VEHSHAM16A</t>
+          <t>AH-RCPL-QA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1754,16 +1754,26 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>AH-PROMARKIT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>AH-MFDRYTWLA</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>3</v>
       </c>
     </row>

--- a/inventory/files/2026-W40/STA_CA_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_CA_AUTO_2026-W40.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1657</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1001</v>
+        <v>991</v>
       </c>
     </row>
     <row r="11">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>795</v>
+        <v>686</v>
       </c>
     </row>
     <row r="12">
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>437</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
